--- a/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
+++ b/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\fuels\FPIEBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/shruti_dayal_wri_org/Documents/Desktop/EPS updated files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E0A33-3857-4E42-99DE-F3DBB58130FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{725982E8-2F86-4DBC-AC68-A6B7F5F118BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18705" yWindow="1695" windowWidth="19470" windowHeight="20340" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="FPIEBP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -61,15 +63,15 @@
     <t>in ways appropriate to each sector (such as by building type and building component in the Buildings Sector, etc.)</t>
   </si>
   <si>
+    <t>Therefore, we cannot alter BAU fuel consumption here.</t>
+  </si>
+  <si>
+    <t>The EPS takes in data for BAU fuel production, imports, and exports, but can only use data for two of those three terms</t>
+  </si>
+  <si>
     <t>for any given fuel.  It must calculate the third of these terms to ensure the equation above holds true.</t>
   </si>
   <si>
-    <t>Therefore, we cannot alter BAU fuel consumption here.</t>
-  </si>
-  <si>
-    <t>The EPS takes in data for BAU fuel production, imports, and exports, but can only use data for two of those three terms</t>
-  </si>
-  <si>
     <t>This variable specifies which of those terms will be calculated, rather than taken in as input data.</t>
   </si>
   <si>
@@ -91,18 +93,24 @@
     <t>the variable designated priority 3 will be altered.</t>
   </si>
   <si>
+    <t>Guidance on Setting Priorities</t>
+  </si>
+  <si>
     <t>Remember that we are setting which variable is calculated in the BAU case, which has nothing to do with policy effects.</t>
   </si>
   <si>
+    <t>The variable to be calculated should generally be the one for which:</t>
+  </si>
+  <si>
     <t>1. you have the lowest-quality (most uncertain) input data</t>
   </si>
   <si>
-    <t>The variable to be calculated should generally be the one for which:</t>
-  </si>
-  <si>
     <t>and</t>
   </si>
   <si>
+    <t>2. the magnitude is large enough to use as a balancing term</t>
+  </si>
+  <si>
     <t>Three examples may help illustrate:</t>
   </si>
   <si>
@@ -130,9 +138,6 @@
     <t>local demand).</t>
   </si>
   <si>
-    <t>2. the magnitude is large enough to use as a balancing term</t>
-  </si>
-  <si>
     <t>Example 3</t>
   </si>
   <si>
@@ -148,7 +153,16 @@
     <t>exceeding import/export capacity.  Only production has a magnitude suitable for use as a balancing term.</t>
   </si>
   <si>
-    <t>Guidance on Setting Priorities</t>
+    <t>Unit: dimensionless (priority)</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>imports</t>
+  </si>
+  <si>
+    <t>exports</t>
   </si>
   <si>
     <t>electricity (not used in this variable)</t>
@@ -212,18 +226,6 @@
   </si>
   <si>
     <t>hydrogen</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (priority)</t>
-  </si>
-  <si>
-    <t>production</t>
-  </si>
-  <si>
-    <t>imports</t>
-  </si>
-  <si>
-    <t>exports</t>
   </si>
 </sst>
 </file>
@@ -287,19 +289,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,14 +614,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290315BF-FDD8-4070-97AB-AF459B926789}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,190 +629,190 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -827,313 +826,312 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
-    <col min="2" max="4" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.26953125" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>59</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>60</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>61</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="7">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="7">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="9">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9">
-        <v>3</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="9">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="9">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="7">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="9">
-        <v>1</v>
-      </c>
-      <c r="C17" s="9">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="9">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="9">
-        <v>1</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="9">
-        <v>1</v>
-      </c>
-      <c r="C20" s="9">
-        <v>3</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="9">
-        <v>1</v>
-      </c>
-      <c r="C21" s="9">
-        <v>3</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
@@ -1146,4 +1144,184 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{629BAA89-44F6-4EE8-BEB1-B89D03CB7DA0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FBFE0EC-04F6-41B4-AD65-1B067E41F13B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58F024EC-357B-4B7A-80FB-FD18CDFC00ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>